--- a/04_Figures/F04_association/modules/T3/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T3/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.21552018669935</v>
+        <v>-19.7363312686323</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0511796666669531</v>
+        <v>-1.5136602437984</v>
       </c>
       <c r="F2" t="n">
-        <v>0.959960398398357</v>
+        <v>0.154039456677045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.959960398398357</v>
+        <v>0.338886804689499</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-24.7176981071866</v>
+        <v>4.14003001931996</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.14589277918116</v>
+        <v>0.291387722337362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0513398576108781</v>
+        <v>0.775352238825111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.137781898587717</v>
+        <v>0.89577545747138</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.4767298334577</v>
+        <v>-27.8162075024465</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.51166767304527</v>
+        <v>-2.23745914784288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0260099300543521</v>
+        <v>0.0434001711876921</v>
       </c>
       <c r="G4" t="n">
-        <v>0.137781898587717</v>
+        <v>0.15249357030476</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1.17540437588845</v>
+        <v>31.7371816397302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0876704661033647</v>
+        <v>2.10356845954511</v>
       </c>
       <c r="F5" t="n">
-        <v>0.931474684920204</v>
+        <v>0.0554522073835491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.959960398398357</v>
+        <v>0.15249357030476</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-13.8942291743769</v>
+        <v>-15.4008922791468</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.90060830188201</v>
+        <v>-1.00633233501638</v>
       </c>
       <c r="F6" t="n">
-        <v>0.384177398107177</v>
+        <v>0.33262030702948</v>
       </c>
       <c r="G6" t="n">
-        <v>0.663547842325782</v>
+        <v>0.585047425037431</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.38139087533674</v>
+        <v>0.711457905514519</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0802463629447038</v>
+        <v>0.0303019908200513</v>
       </c>
       <c r="F7" t="n">
-        <v>0.937263522779694</v>
+        <v>0.976286480409309</v>
       </c>
       <c r="G7" t="n">
-        <v>0.959960398398357</v>
+        <v>0.976286480409309</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13.0281980789632</v>
+        <v>27.3275683529801</v>
       </c>
       <c r="E8" t="n">
-        <v>0.854429495406216</v>
+        <v>2.63411250733989</v>
       </c>
       <c r="F8" t="n">
-        <v>0.408337133738943</v>
+        <v>0.0206255601412881</v>
       </c>
       <c r="G8" t="n">
-        <v>0.663547842325782</v>
+        <v>0.119535965070277</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>27.9747922501031</v>
+        <v>-4.17327349949859</v>
       </c>
       <c r="E9" t="n">
-        <v>2.44760911516507</v>
+        <v>-0.239646600921368</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0293445120287485</v>
+        <v>0.814341324973982</v>
       </c>
       <c r="G9" t="n">
-        <v>0.137781898587717</v>
+        <v>0.89577545747138</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>32.4145839484374</v>
+        <v>-18.4204749635253</v>
       </c>
       <c r="E10" t="n">
-        <v>2.24848027300854</v>
+        <v>-0.924033472097164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0425265811139684</v>
+        <v>0.372302906842002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.137781898587717</v>
+        <v>0.585047425037431</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>2.18785187326066</v>
+        <v>12.6379138164657</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0868466781057207</v>
+        <v>0.811885623384677</v>
       </c>
       <c r="F11" t="n">
-        <v>0.932116828045777</v>
+        <v>0.431472941811587</v>
       </c>
       <c r="G11" t="n">
-        <v>0.959960398398357</v>
+        <v>0.593275294990932</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>24.0771359280543</v>
+        <v>-30.6438272632077</v>
       </c>
       <c r="E12" t="n">
-        <v>2.12851080670989</v>
+        <v>-2.60655806043714</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0529930379183529</v>
+        <v>0.0217338118309594</v>
       </c>
       <c r="G12" t="n">
-        <v>0.137781898587717</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.8397926447757</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.752506417492371</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.465155113838008</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.671890719988234</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-18.8045843243761</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.04460231935995</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.315242836447182</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.663547842325782</v>
+        <v>0.119535965070277</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2448.64699537858</v>
+        <v>-585.302820555413</v>
       </c>
       <c r="E2" t="n">
-        <v>0.616893095816335</v>
+        <v>-0.244691309148506</v>
       </c>
       <c r="F2" t="n">
-        <v>0.547957619870723</v>
+        <v>0.810515293948745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.791494339813267</v>
+        <v>0.886507138092488</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-1491.38263888364</v>
+        <v>-1956.61379370589</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.667401032030158</v>
+        <v>-0.830846727652684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.516188861783324</v>
+        <v>0.421058157799097</v>
       </c>
       <c r="G3" t="n">
-        <v>0.791494339813267</v>
+        <v>0.877679303912976</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-3142.32079066742</v>
+        <v>-1945.49333788651</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.38864735647637</v>
+        <v>-0.803525321563599</v>
       </c>
       <c r="F4" t="n">
-        <v>0.188273733019131</v>
+        <v>0.436117679101924</v>
       </c>
       <c r="G4" t="n">
-        <v>0.791494339813267</v>
+        <v>0.877679303912976</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-2238.10644730502</v>
+        <v>1849.30670517521</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0232097002326</v>
+        <v>0.634048846949703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.324872947782637</v>
+        <v>0.537046557867901</v>
       </c>
       <c r="G5" t="n">
-        <v>0.791494339813267</v>
+        <v>0.877679303912976</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>785.435785325994</v>
+        <v>594.329498929001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2922933799724</v>
+        <v>0.221042051534357</v>
       </c>
       <c r="F6" t="n">
-        <v>0.774675052573385</v>
+        <v>0.82849361668165</v>
       </c>
       <c r="G6" t="n">
-        <v>0.880561987676613</v>
+        <v>0.886507138092488</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>1133.01980454855</v>
+        <v>2357.81630471152</v>
       </c>
       <c r="E7" t="n">
-        <v>0.390387939378243</v>
+        <v>0.600459726636918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.702571520951418</v>
+        <v>0.558523193399167</v>
       </c>
       <c r="G7" t="n">
-        <v>0.880561987676613</v>
+        <v>0.877679303912976</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>3031.7909455222</v>
+        <v>3769.9853578815</v>
       </c>
       <c r="E8" t="n">
-        <v>1.20302525676342</v>
+        <v>1.9728572886807</v>
       </c>
       <c r="F8" t="n">
-        <v>0.250418808381466</v>
+        <v>0.0701625967397685</v>
       </c>
       <c r="G8" t="n">
-        <v>0.791494339813267</v>
+        <v>0.771788564137453</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4235.65403933391</v>
+        <v>1391.66426866656</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0905195973098</v>
+        <v>0.474378763514963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0567806897740752</v>
+        <v>0.643099156368794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.738148967062978</v>
+        <v>0.884261340007092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1964.43828997944</v>
+        <v>-2688.45880121393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.694528697861241</v>
+        <v>-0.788778692903444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.499575705557271</v>
+        <v>0.444388721175124</v>
       </c>
       <c r="G10" t="n">
-        <v>0.791494339813267</v>
+        <v>0.877679303912976</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>1030.0665881795</v>
+        <v>393.423861598126</v>
       </c>
       <c r="E11" t="n">
-        <v>0.241643208044451</v>
+        <v>0.14555268904222</v>
       </c>
       <c r="F11" t="n">
-        <v>0.812826450163027</v>
+        <v>0.886507138092488</v>
       </c>
       <c r="G11" t="n">
-        <v>0.880561987676613</v>
+        <v>0.886507138092488</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>1437.51876327231</v>
+        <v>-3197.47011609927</v>
       </c>
       <c r="E12" t="n">
-        <v>0.656082809232956</v>
+        <v>-1.39381129959883</v>
       </c>
       <c r="F12" t="n">
-        <v>0.523214027967375</v>
+        <v>0.186743915655367</v>
       </c>
       <c r="G12" t="n">
-        <v>0.791494339813267</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>313.082856165446</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.114951408727837</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.910240176555188</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.910240176555188</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-2573.27907752519</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.831073790705037</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.420934445660385</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.791494339813267</v>
+        <v>0.877679303912976</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1644.84547012377</v>
+        <v>-994.070918748174</v>
       </c>
       <c r="E2" t="n">
-        <v>0.442363646418587</v>
+        <v>-0.449151715910071</v>
       </c>
       <c r="F2" t="n">
-        <v>0.665496506327557</v>
+        <v>0.660718712391221</v>
       </c>
       <c r="G2" t="n">
-        <v>0.87349012524289</v>
+        <v>0.914816249264115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-1637.35950271792</v>
+        <v>-1872.48876751234</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.793005167634191</v>
+        <v>-0.856051903657843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.442007999091219</v>
+        <v>0.4074714720757</v>
       </c>
       <c r="G3" t="n">
-        <v>0.759690526422</v>
+        <v>0.794709693194876</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-2703.85495506925</v>
+        <v>-1876.96418773056</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.27090521049667</v>
+        <v>-0.834899081222267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.226033976902506</v>
+        <v>0.418853878897486</v>
       </c>
       <c r="G4" t="n">
-        <v>0.759690526422</v>
+        <v>0.794709693194876</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-2091.36006641758</v>
+        <v>2172.7861445144</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.02816168167306</v>
+        <v>0.808269484768817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.32262490143141</v>
+        <v>0.433478014469933</v>
       </c>
       <c r="G5" t="n">
-        <v>0.759690526422</v>
+        <v>0.794709693194876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-28.3665007288438</v>
+        <v>-140.319431206838</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.011310596216587</v>
+        <v>-0.0560008890464785</v>
       </c>
       <c r="F6" t="n">
-        <v>0.991147377398854</v>
+        <v>0.956192652464746</v>
       </c>
       <c r="G6" t="n">
-        <v>0.991147377398854</v>
+        <v>0.956192652464746</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>997.295913652436</v>
+        <v>1540.44944333851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.369154539141186</v>
+        <v>0.418776551097329</v>
       </c>
       <c r="F7" t="n">
-        <v>0.717955444143504</v>
+        <v>0.682215689921121</v>
       </c>
       <c r="G7" t="n">
-        <v>0.87349012524289</v>
+        <v>0.914816249264115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>2220.03018625015</v>
+        <v>3363.5338763061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.927511176686033</v>
+        <v>1.86978377054282</v>
       </c>
       <c r="F8" t="n">
-        <v>0.370561917457345</v>
+        <v>0.0842002172649754</v>
       </c>
       <c r="G8" t="n">
-        <v>0.759690526422</v>
+        <v>0.794709693194876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>3687.62095351099</v>
+        <v>497.540159181011</v>
       </c>
       <c r="E9" t="n">
-        <v>1.91687432797882</v>
+        <v>0.180979878922371</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0774972888859404</v>
+        <v>0.859174446492441</v>
       </c>
       <c r="G9" t="n">
-        <v>0.759690526422</v>
+        <v>0.945091891141685</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>2183.05327332458</v>
+        <v>-3606.15681211364</v>
       </c>
       <c r="E10" t="n">
-        <v>0.836327133713388</v>
+        <v>-1.16789056769616</v>
       </c>
       <c r="F10" t="n">
-        <v>0.418078902277415</v>
+        <v>0.263824518400842</v>
       </c>
       <c r="G10" t="n">
-        <v>0.759690526422</v>
+        <v>0.794709693194876</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>992.243017017236</v>
+        <v>820.844916681291</v>
       </c>
       <c r="E11" t="n">
-        <v>0.250258894485105</v>
+        <v>0.327524095942626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.806298577147283</v>
+        <v>0.748486022125185</v>
       </c>
       <c r="G11" t="n">
-        <v>0.87349012524289</v>
+        <v>0.914816249264115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>1518.27535110745</v>
+        <v>-2808.4343616385</v>
       </c>
       <c r="E12" t="n">
-        <v>0.748471733514978</v>
+        <v>-1.30544745089739</v>
       </c>
       <c r="F12" t="n">
-        <v>0.467501862413538</v>
+        <v>0.214372485130422</v>
       </c>
       <c r="G12" t="n">
-        <v>0.759690526422</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>759.773281020209</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.300757057503255</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.768355858917791</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.87349012524289</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-3329.7449742781</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.18581485499897</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.256917676415509</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.759690526422</v>
+        <v>0.794709693194876</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.48749285720733</v>
+        <v>-5.50187255817476</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.3490088573857</v>
+        <v>-2.07706384647581</v>
       </c>
       <c r="F2" t="n">
-        <v>0.200363365764207</v>
+        <v>0.0581815298509674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3721033935621</v>
+        <v>0.127999365672128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.54696767300704</v>
+        <v>6.14967609046337</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.25897051523313</v>
+        <v>2.39630732865672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0417105190485935</v>
+        <v>0.0323075219165712</v>
       </c>
       <c r="G3" t="n">
-        <v>0.135559186907929</v>
+        <v>0.127999365672128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.96207534360454</v>
+        <v>-5.75358982487338</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.37095272072772</v>
+        <v>-2.10689028061699</v>
       </c>
       <c r="F4" t="n">
-        <v>0.19359430292377</v>
+        <v>0.0551186675417006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3721033935621</v>
+        <v>0.127999365672128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>5.77239329007417</v>
+        <v>7.77655437406336</v>
       </c>
       <c r="E5" t="n">
-        <v>2.38827247323077</v>
+        <v>2.50907092052229</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0327967878952768</v>
+        <v>0.0261376979937878</v>
       </c>
       <c r="G5" t="n">
-        <v>0.135559186907929</v>
+        <v>0.127999365672128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.17193549755562</v>
+        <v>-6.35904782098669</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.07043364178686</v>
+        <v>-2.15752592333068</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0588835180026033</v>
+        <v>0.0502605074385902</v>
       </c>
       <c r="G6" t="n">
-        <v>0.153097146806769</v>
+        <v>0.127999365672128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.01029055389591</v>
+        <v>-6.4033455992772</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.829880634764744</v>
+        <v>-1.34669244245678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.421584786852894</v>
+        <v>0.201089063282297</v>
       </c>
       <c r="G7" t="n">
-        <v>0.595125041565191</v>
+        <v>0.31599709944361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.754365355783753</v>
+        <v>2.06351807812954</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.223118563409722</v>
+        <v>0.759249703801848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.826910841832864</v>
+        <v>0.461249318454818</v>
       </c>
       <c r="G8" t="n">
-        <v>0.826910841832864</v>
+        <v>0.5073742503003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1.50637299408232</v>
+        <v>-3.05271048575766</v>
       </c>
       <c r="E9" t="n">
-        <v>0.509444452647536</v>
+        <v>-0.830309746608487</v>
       </c>
       <c r="F9" t="n">
-        <v>0.618978128494121</v>
+        <v>0.421350819403959</v>
       </c>
       <c r="G9" t="n">
-        <v>0.731519606402143</v>
+        <v>0.5073742503003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>8.019782426363</v>
+        <v>2.17284528321413</v>
       </c>
       <c r="E10" t="n">
-        <v>2.74406454863502</v>
+        <v>0.492970195962876</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0167264447729797</v>
+        <v>0.630255649035039</v>
       </c>
       <c r="G10" t="n">
-        <v>0.135559186907929</v>
+        <v>0.630255649035039</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.41347363758293</v>
+        <v>2.77398544890178</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.83145217466632</v>
+        <v>0.825014417991608</v>
       </c>
       <c r="F11" t="n">
-        <v>0.420728341467435</v>
+        <v>0.424243987339621</v>
       </c>
       <c r="G11" t="n">
-        <v>0.595125041565191</v>
+        <v>0.5073742503003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>5.68993358035718</v>
+        <v>-4.34145266998467</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4102593292635</v>
+        <v>-1.49931659670644</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0314744888171291</v>
+        <v>0.157679352932126</v>
       </c>
       <c r="G12" t="n">
-        <v>0.135559186907929</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.60096110636285</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.765254642121651</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.457788493511685</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.595125041565191</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.14569216969812</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.283654266131175</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.78114250010798</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.826910841832864</v>
+        <v>0.289078813708898</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>22.6828201801744</v>
+        <v>31.6953098820755</v>
       </c>
       <c r="E2" t="n">
-        <v>0.256321284517077</v>
+        <v>0.608568625867339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.801714270783289</v>
+        <v>0.553295876113209</v>
       </c>
       <c r="G2" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>23.0490766217915</v>
+        <v>24.8675037575867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.464172911316564</v>
+        <v>0.471045346539944</v>
       </c>
       <c r="F3" t="n">
-        <v>0.650201095846174</v>
+        <v>0.645414814256874</v>
       </c>
       <c r="G3" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-31.5743314592635</v>
+        <v>11.6901693921271</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.599143723016751</v>
+        <v>0.214291760358843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.559374068628081</v>
+        <v>0.833644226422968</v>
       </c>
       <c r="G4" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>24.1442889786592</v>
+        <v>-56.1084956076919</v>
       </c>
       <c r="E5" t="n">
-        <v>0.486372900386406</v>
+        <v>-0.885570787672091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634799250879155</v>
+        <v>0.391935380820373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>34.6574066622357</v>
+        <v>35.963792776158</v>
       </c>
       <c r="E6" t="n">
-        <v>0.591316406394484</v>
+        <v>0.614745895543723</v>
       </c>
       <c r="F6" t="n">
-        <v>0.564449401028801</v>
+        <v>0.549331831844173</v>
       </c>
       <c r="G6" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-15.4874156916811</v>
+        <v>25.403296230953</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.24135285713043</v>
+        <v>0.290605743674234</v>
       </c>
       <c r="F7" t="n">
-        <v>0.813046697991032</v>
+        <v>0.77593710061624</v>
       </c>
       <c r="G7" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2322969350702</v>
+        <v>8.68543194251865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.539562909754486</v>
+        <v>0.181216994512471</v>
       </c>
       <c r="F8" t="n">
-        <v>0.598619173217898</v>
+        <v>0.8589921003139</v>
       </c>
       <c r="G8" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>16.1080248143057</v>
+        <v>52.4224322359435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.313366933963279</v>
+        <v>0.824966354966768</v>
       </c>
       <c r="F9" t="n">
-        <v>0.758973004138299</v>
+        <v>0.424270306555355</v>
       </c>
       <c r="G9" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-45.2677624737801</v>
+        <v>97.7760743829988</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.727737679494392</v>
+        <v>1.35947899113779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.479676986496551</v>
+        <v>0.197109865681296</v>
       </c>
       <c r="G10" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>51.0906750688805</v>
+        <v>-47.414047035927</v>
       </c>
       <c r="E11" t="n">
-        <v>0.549073832770319</v>
+        <v>-0.815692331579144</v>
       </c>
       <c r="F11" t="n">
-        <v>0.592261330017703</v>
+        <v>0.429368711541576</v>
       </c>
       <c r="G11" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>3.94556614476279</v>
+        <v>-26.772437425745</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0804384391536019</v>
+        <v>-0.498808433583029</v>
       </c>
       <c r="F12" t="n">
-        <v>0.937113705851424</v>
+        <v>0.626247817403392</v>
       </c>
       <c r="G12" t="n">
-        <v>0.937113705851424</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-49.4369205362655</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.84585132933158</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.412934494284971</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.880800589490284</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>92.0811817237282</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.4127727471253</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.181214462596328</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.880800589490284</v>
+        <v>0.8589921003139</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>6.805132508332</v>
+        <v>-0.595363852091916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.350727124930236</v>
+        <v>-0.0517079885718878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.731873088937065</v>
+        <v>0.959612154392913</v>
       </c>
       <c r="G2" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.37330183702709</v>
+        <v>-4.17699711740554</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.312909936896358</v>
+        <v>-0.353027829112147</v>
       </c>
       <c r="F3" t="n">
-        <v>0.759720506142556</v>
+        <v>0.73019124635806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0826357378788522</v>
+        <v>-4.19336216728976</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.00723435828995584</v>
+        <v>-0.354992412222112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.994346745250076</v>
+        <v>0.72875627083443</v>
       </c>
       <c r="G4" t="n">
-        <v>0.994346745250076</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.23349754590633</v>
+        <v>9.92704884048234</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.373630874990829</v>
+        <v>0.719682867799796</v>
       </c>
       <c r="F5" t="n">
-        <v>0.715196374287334</v>
+        <v>0.485501449996265</v>
       </c>
       <c r="G5" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.74578158307359</v>
+        <v>-3.13460541117894</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.132312974316361</v>
+        <v>-0.23834499701179</v>
       </c>
       <c r="F6" t="n">
-        <v>0.896929440324239</v>
+        <v>0.8156349562496</v>
       </c>
       <c r="G6" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>7.33443280778093</v>
+        <v>6.09081737333405</v>
       </c>
       <c r="E7" t="n">
-        <v>0.488593671651267</v>
+        <v>0.31767302807157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.633936406537755</v>
+        <v>0.756192719632987</v>
       </c>
       <c r="G7" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>10.0926877957364</v>
+        <v>9.5460365153422</v>
       </c>
       <c r="E8" t="n">
-        <v>0.828198331685127</v>
+        <v>0.961346410887922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.423724233559906</v>
+        <v>0.355349707964864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>9.9881893907427</v>
+        <v>6.78359293601682</v>
       </c>
       <c r="E9" t="n">
-        <v>0.938670972970539</v>
+        <v>0.491807120612546</v>
       </c>
       <c r="F9" t="n">
-        <v>0.366409657274133</v>
+        <v>0.631728887631578</v>
       </c>
       <c r="G9" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>8.91426133178106</v>
+        <v>-2.3443377237794</v>
       </c>
       <c r="E10" t="n">
-        <v>0.663502699757244</v>
+        <v>-0.140023377879371</v>
       </c>
       <c r="F10" t="n">
-        <v>0.519552311880687</v>
+        <v>0.890964306842147</v>
       </c>
       <c r="G10" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.516744730735</v>
+        <v>-1.41052436951805</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.652662404977734</v>
+        <v>-0.108683172270541</v>
       </c>
       <c r="F11" t="n">
-        <v>0.526279920419036</v>
+        <v>0.915249985132096</v>
       </c>
       <c r="G11" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2.47198484346512</v>
+        <v>-2.20158139944738</v>
       </c>
       <c r="E12" t="n">
-        <v>0.236468751444195</v>
+        <v>-0.190046403858476</v>
       </c>
       <c r="F12" t="n">
-        <v>0.817057168904937</v>
+        <v>0.852449706744467</v>
       </c>
       <c r="G12" t="n">
-        <v>0.991502587952216</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.4208734826293</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.108704843447995</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.915233158109738</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.991502587952216</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-4.41124334728713</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.290661318777875</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.776272617459164</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.991502587952216</v>
+        <v>0.959612154392913</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -2501,24 +2219,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>13.8942291743769</v>
+        <v>18.4204749635253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.41124334728713</v>
+        <v>4.17699711740554</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>31.2322969350702</v>
+        <v>31.6953098820755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1964.43828997944</v>
+        <v>1945.49333788651</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,33 +2323,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1644.84547012377</v>
+        <v>1872.48876751234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.41347363758293</v>
+        <v>5.50187255817476</v>
       </c>
     </row>
   </sheetData>
